--- a/saida/concilia_cupom.xlsx
+++ b/saida/concilia_cupom.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1937" uniqueCount="567">
   <si>
     <t>Tipo</t>
   </si>
@@ -248,9 +248,6 @@
     <t>7582</t>
   </si>
   <si>
-    <t>17779</t>
-  </si>
-  <si>
     <t>17927</t>
   </si>
   <si>
@@ -278,7 +275,7 @@
     <t>43873</t>
   </si>
   <si>
-    <t>41521</t>
+    <t>41522</t>
   </si>
   <si>
     <t>04:45</t>
@@ -419,9 +416,6 @@
     <t>21:57</t>
   </si>
   <si>
-    <t>23:59</t>
-  </si>
-  <si>
     <t>21:48</t>
   </si>
   <si>
@@ -677,9 +671,6 @@
     <t>Débito 47.25</t>
   </si>
   <si>
-    <t>PIX 52.40</t>
-  </si>
-  <si>
     <t>Débito 14.90</t>
   </si>
   <si>
@@ -860,9 +851,6 @@
     <t>Débito 15.75 (00:08) + Débito 15.75 (00:07) + Débito 15.75 (00:07)</t>
   </si>
   <si>
-    <t>Débito 52.40 (00:01)</t>
-  </si>
-  <si>
     <t>Crédito 14.90 (21:49)</t>
   </si>
   <si>
@@ -1043,9 +1031,6 @@
     <t>6FSHQH + 905335 + KG3AZP</t>
   </si>
   <si>
-    <t>858205</t>
-  </si>
-  <si>
     <t>7BMSLY</t>
   </si>
   <si>
@@ -1316,9 +1301,6 @@
     <t>00:07:14</t>
   </si>
   <si>
-    <t>00:01:54</t>
-  </si>
-  <si>
     <t>21:49:29</t>
   </si>
   <si>
@@ -1695,9 +1677,6 @@
   </si>
   <si>
     <t>APT88F1E</t>
-  </si>
-  <si>
-    <t>APT9B7FF</t>
   </si>
   <si>
     <t>APT9B804</t>
@@ -2072,7 +2051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2124,25 +2103,25 @@
         <v>27</v>
       </c>
       <c r="D2" s="1">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="E2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G2">
         <v>28.4</v>
       </c>
       <c r="H2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="J2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -2162,25 +2141,25 @@
         <v>28</v>
       </c>
       <c r="D3" s="1">
-        <v>46300</v>
+        <v>46299</v>
       </c>
       <c r="E3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G3">
         <v>66.09999999999999</v>
       </c>
       <c r="H3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="J3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -2200,25 +2179,25 @@
         <v>29</v>
       </c>
       <c r="D4" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="E4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G4">
         <v>25.7</v>
       </c>
       <c r="H4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="J4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -2238,25 +2217,25 @@
         <v>30</v>
       </c>
       <c r="D5" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="E5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G5">
         <v>74.5</v>
       </c>
       <c r="H5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="J5" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -2276,25 +2255,25 @@
         <v>31</v>
       </c>
       <c r="D6" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G6">
         <v>56.75</v>
       </c>
       <c r="H6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="J6" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -2314,25 +2293,25 @@
         <v>32</v>
       </c>
       <c r="D7" s="1">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="E7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G7">
         <v>37</v>
       </c>
       <c r="H7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="J7" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -2355,22 +2334,22 @@
         <v>46308</v>
       </c>
       <c r="E8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G8">
         <v>47.9</v>
       </c>
       <c r="H8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I8" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="J8" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -2390,25 +2369,25 @@
         <v>34</v>
       </c>
       <c r="D9" s="1">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="E9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G9">
         <v>163.59</v>
       </c>
       <c r="H9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J9" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -2431,22 +2410,22 @@
         <v>46300</v>
       </c>
       <c r="E10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G10">
         <v>74.90000000000001</v>
       </c>
       <c r="H10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I10" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="J10" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -2469,22 +2448,22 @@
         <v>46300</v>
       </c>
       <c r="E11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G11">
         <v>31.5</v>
       </c>
       <c r="H11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I11" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="J11" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -2507,22 +2486,22 @@
         <v>46304</v>
       </c>
       <c r="E12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G12">
         <v>101.9</v>
       </c>
       <c r="H12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I12" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="J12" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -2545,22 +2524,22 @@
         <v>46306</v>
       </c>
       <c r="E13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G13">
         <v>45.3</v>
       </c>
       <c r="H13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I13" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="J13" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -2583,22 +2562,22 @@
         <v>46309</v>
       </c>
       <c r="E14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F14" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G14">
         <v>75.59999999999999</v>
       </c>
       <c r="H14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I14" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="J14" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -2618,25 +2597,25 @@
         <v>40</v>
       </c>
       <c r="D15" s="1">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="E15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G15">
         <v>58.75</v>
       </c>
       <c r="H15" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I15" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="J15" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -2659,22 +2638,22 @@
         <v>46301</v>
       </c>
       <c r="E16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G16">
         <v>102.48</v>
       </c>
       <c r="H16" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I16" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J16" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -2694,25 +2673,25 @@
         <v>42</v>
       </c>
       <c r="D17" s="1">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="E17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G17">
         <v>90</v>
       </c>
       <c r="H17" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I17" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="J17" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -2732,25 +2711,25 @@
         <v>43</v>
       </c>
       <c r="D18" s="1">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="E18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F18" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G18">
         <v>62.89</v>
       </c>
       <c r="H18" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I18" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="J18" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -2773,22 +2752,22 @@
         <v>46309</v>
       </c>
       <c r="E19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G19">
         <v>20</v>
       </c>
       <c r="H19" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I19" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J19" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -2811,22 +2790,22 @@
         <v>46298</v>
       </c>
       <c r="E20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F20" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G20">
         <v>31.5</v>
       </c>
       <c r="H20" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I20" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J20" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -2849,22 +2828,22 @@
         <v>46300</v>
       </c>
       <c r="E21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F21" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G21">
         <v>44.8</v>
       </c>
       <c r="H21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I21" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="J21" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -2887,22 +2866,22 @@
         <v>46303</v>
       </c>
       <c r="E22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F22" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G22">
         <v>47.8</v>
       </c>
       <c r="H22" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I22" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J22" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -2925,22 +2904,22 @@
         <v>46303</v>
       </c>
       <c r="E23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F23" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G23">
         <v>18.75</v>
       </c>
       <c r="H23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I23" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="J23" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -2963,22 +2942,22 @@
         <v>46298</v>
       </c>
       <c r="E24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F24" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G24">
         <v>37.9</v>
       </c>
       <c r="H24" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I24" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="J24" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -3001,22 +2980,22 @@
         <v>46301</v>
       </c>
       <c r="E25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F25" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G25">
         <v>64.2</v>
       </c>
       <c r="H25" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I25" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="J25" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -3039,22 +3018,22 @@
         <v>46309</v>
       </c>
       <c r="E26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F26" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G26">
         <v>49.8</v>
       </c>
       <c r="H26" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I26" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="J26" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -3074,25 +3053,25 @@
         <v>52</v>
       </c>
       <c r="D27" s="1">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="E27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F27" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G27">
         <v>68.3</v>
       </c>
       <c r="H27" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I27" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J27" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -3115,22 +3094,22 @@
         <v>46296</v>
       </c>
       <c r="E28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F28" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G28">
         <v>49.15</v>
       </c>
       <c r="H28" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I28" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="J28" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -3153,22 +3132,22 @@
         <v>46301</v>
       </c>
       <c r="E29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F29" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G29">
         <v>89.67</v>
       </c>
       <c r="H29" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I29" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="J29" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -3191,22 +3170,22 @@
         <v>46303</v>
       </c>
       <c r="E30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F30" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G30">
         <v>117.84</v>
       </c>
       <c r="H30" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I30" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="J30" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -3226,25 +3205,25 @@
         <v>56</v>
       </c>
       <c r="D31" s="1">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="E31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F31" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G31">
         <v>62.25</v>
       </c>
       <c r="H31" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I31" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="J31" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="K31">
         <v>2</v>
@@ -3267,22 +3246,22 @@
         <v>46296</v>
       </c>
       <c r="E32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F32" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G32">
         <v>93.2</v>
       </c>
       <c r="H32" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I32" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="J32" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -3302,25 +3281,25 @@
         <v>58</v>
       </c>
       <c r="D33" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="E33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F33" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G33">
         <v>41</v>
       </c>
       <c r="H33" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I33" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="J33" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -3340,25 +3319,25 @@
         <v>59</v>
       </c>
       <c r="D34" s="1">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="E34" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F34" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G34">
         <v>27.5</v>
       </c>
       <c r="H34" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I34" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="J34" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="K34">
         <v>1</v>
@@ -3381,22 +3360,22 @@
         <v>46298</v>
       </c>
       <c r="E35" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F35" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G35">
         <v>70.3</v>
       </c>
       <c r="H35" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I35" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="J35" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="K35">
         <v>2</v>
@@ -3419,22 +3398,22 @@
         <v>46301</v>
       </c>
       <c r="E36" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F36" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G36">
         <v>16.75</v>
       </c>
       <c r="H36" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I36" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="J36" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="K36">
         <v>1</v>
@@ -3457,22 +3436,22 @@
         <v>46300</v>
       </c>
       <c r="E37" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F37" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G37">
         <v>74.8</v>
       </c>
       <c r="H37" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I37" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="J37" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -3495,22 +3474,22 @@
         <v>46300</v>
       </c>
       <c r="E38" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F38" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G38">
         <v>58.2</v>
       </c>
       <c r="H38" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="J38" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="K38">
         <v>1</v>
@@ -3533,22 +3512,22 @@
         <v>46300</v>
       </c>
       <c r="E39" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F39" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G39">
         <v>39</v>
       </c>
       <c r="H39" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I39" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="J39" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="K39">
         <v>1</v>
@@ -3571,22 +3550,22 @@
         <v>46300</v>
       </c>
       <c r="E40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F40" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G40">
         <v>73.2</v>
       </c>
       <c r="H40" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I40" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="J40" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="K40">
         <v>2</v>
@@ -3606,25 +3585,25 @@
         <v>66</v>
       </c>
       <c r="D41" s="1">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="E41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F41" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G41">
         <v>75.3</v>
       </c>
       <c r="H41" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I41" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="J41" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="K41">
         <v>1</v>
@@ -3647,22 +3626,22 @@
         <v>46305</v>
       </c>
       <c r="E42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F42" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G42">
         <v>7.9</v>
       </c>
       <c r="H42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I42" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="J42" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="K42">
         <v>1</v>
@@ -3685,22 +3664,22 @@
         <v>46306</v>
       </c>
       <c r="E43" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F43" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G43">
         <v>50</v>
       </c>
       <c r="H43" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I43" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="J43" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="K43">
         <v>1</v>
@@ -3723,22 +3702,22 @@
         <v>46307</v>
       </c>
       <c r="E44" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F44" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G44">
         <v>38</v>
       </c>
       <c r="H44" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I44" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="J44" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="K44">
         <v>1</v>
@@ -3761,22 +3740,22 @@
         <v>46296</v>
       </c>
       <c r="E45" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F45" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G45">
         <v>50.25</v>
       </c>
       <c r="H45" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I45" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="J45" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="K45">
         <v>1</v>
@@ -3799,22 +3778,22 @@
         <v>46305</v>
       </c>
       <c r="E46" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F46" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G46">
         <v>9.220000000000001</v>
       </c>
       <c r="H46" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I46" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="J46" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="K46">
         <v>1</v>
@@ -3837,22 +3816,22 @@
         <v>46297</v>
       </c>
       <c r="E47" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F47" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G47">
         <v>54.05</v>
       </c>
       <c r="H47" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I47" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J47" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="K47">
         <v>1</v>
@@ -3875,22 +3854,22 @@
         <v>46297</v>
       </c>
       <c r="E48" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F48" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G48">
         <v>20.25</v>
       </c>
       <c r="H48" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I48" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="J48" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="K48">
         <v>1</v>
@@ -3913,22 +3892,22 @@
         <v>46297</v>
       </c>
       <c r="E49" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F49" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G49">
         <v>54.3</v>
       </c>
       <c r="H49" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I49" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J49" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="K49">
         <v>1</v>
@@ -3951,22 +3930,22 @@
         <v>46305</v>
       </c>
       <c r="E50" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F50" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G50">
         <v>70.40000000000001</v>
       </c>
       <c r="H50" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I50" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="J50" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="K50">
         <v>1</v>
@@ -3986,25 +3965,25 @@
         <v>76</v>
       </c>
       <c r="D51" s="1">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="E51" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F51" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G51">
         <v>47.25</v>
       </c>
       <c r="H51" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I51" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J51" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="K51">
         <v>1</v>
@@ -4024,25 +4003,25 @@
         <v>77</v>
       </c>
       <c r="D52" s="1">
-        <v>46301</v>
+        <v>46305</v>
       </c>
       <c r="E52" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F52" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G52">
-        <v>52.4</v>
+        <v>14.9</v>
       </c>
       <c r="H52" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I52" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="J52" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="K52">
         <v>1</v>
@@ -4053,7 +4032,7 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B53" t="s">
         <v>22</v>
@@ -4062,69 +4041,69 @@
         <v>78</v>
       </c>
       <c r="D53" s="1">
-        <v>46305</v>
+        <v>46298</v>
       </c>
       <c r="E53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F53" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G53">
-        <v>14.9</v>
+        <v>86.18000000000001</v>
       </c>
       <c r="H53" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I53" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="J53" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="K53">
         <v>1</v>
       </c>
       <c r="L53">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C54" t="s">
         <v>79</v>
       </c>
       <c r="D54" s="1">
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="E54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F54" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G54">
-        <v>86.18000000000001</v>
+        <v>23.65</v>
       </c>
       <c r="H54" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I54" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J54" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="K54">
         <v>1</v>
       </c>
       <c r="L54">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -4138,25 +4117,25 @@
         <v>80</v>
       </c>
       <c r="D55" s="1">
-        <v>46302</v>
+        <v>46296</v>
       </c>
       <c r="E55" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="F55" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G55">
-        <v>23.65</v>
+        <v>33</v>
       </c>
       <c r="H55" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I55" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="J55" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="K55">
         <v>1</v>
@@ -4176,25 +4155,25 @@
         <v>81</v>
       </c>
       <c r="D56" s="1">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="E56" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="F56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G56">
-        <v>33</v>
+        <v>42.6</v>
       </c>
       <c r="H56" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I56" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J56" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="K56">
         <v>1</v>
@@ -4214,25 +4193,25 @@
         <v>82</v>
       </c>
       <c r="D57" s="1">
-        <v>46296</v>
+        <v>46302</v>
       </c>
       <c r="E57" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F57" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G57">
-        <v>42.6</v>
+        <v>9.9</v>
       </c>
       <c r="H57" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I57" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="J57" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="K57">
         <v>1</v>
@@ -4243,40 +4222,40 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C58" t="s">
         <v>83</v>
       </c>
       <c r="D58" s="1">
-        <v>46302</v>
+        <v>46296</v>
       </c>
       <c r="E58" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G58">
-        <v>9.9</v>
+        <v>45.3</v>
       </c>
       <c r="H58" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I58" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="J58" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="K58">
         <v>1</v>
       </c>
       <c r="L58">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -4284,31 +4263,31 @@
         <v>13</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C59" t="s">
         <v>84</v>
       </c>
       <c r="D59" s="1">
-        <v>46296</v>
+        <v>46304</v>
       </c>
       <c r="E59" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F59" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G59">
-        <v>45.3</v>
+        <v>46</v>
       </c>
       <c r="H59" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I59" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="J59" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="K59">
         <v>1</v>
@@ -4328,25 +4307,25 @@
         <v>85</v>
       </c>
       <c r="D60" s="1">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="E60" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F60" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G60">
-        <v>46</v>
+        <v>144.5</v>
       </c>
       <c r="H60" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I60" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="J60" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="K60">
         <v>1</v>
@@ -4357,77 +4336,39 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C61" t="s">
         <v>86</v>
       </c>
       <c r="D61" s="1">
-        <v>46307</v>
+        <v>46301</v>
       </c>
       <c r="E61" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F61" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G61">
-        <v>144.5</v>
+        <v>53.9</v>
       </c>
       <c r="H61" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I61" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="J61" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="K61">
         <v>1</v>
       </c>
       <c r="L61">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12">
-      <c r="A62" t="s">
-        <v>12</v>
-      </c>
-      <c r="B62" t="s">
-        <v>26</v>
-      </c>
-      <c r="C62" t="s">
-        <v>87</v>
-      </c>
-      <c r="D62" s="1">
-        <v>46301</v>
-      </c>
-      <c r="E62" t="s">
-        <v>143</v>
-      </c>
-      <c r="F62" t="s">
-        <v>169</v>
-      </c>
-      <c r="G62">
-        <v>53.9</v>
-      </c>
-      <c r="H62" t="s">
-        <v>230</v>
-      </c>
-      <c r="I62" t="s">
-        <v>291</v>
-      </c>
-      <c r="J62" t="s">
-        <v>352</v>
-      </c>
-      <c r="K62">
-        <v>1</v>
-      </c>
-      <c r="L62">
         <v>1</v>
       </c>
     </row>
@@ -4438,7 +4379,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q144"/>
+  <dimension ref="A1:Q142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -4446,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -4455,7 +4396,7 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -4464,34 +4405,34 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="I1" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
       </c>
       <c r="K1" t="s">
+        <v>352</v>
+      </c>
+      <c r="L1" t="s">
+        <v>353</v>
+      </c>
+      <c r="M1" t="s">
+        <v>354</v>
+      </c>
+      <c r="N1" t="s">
+        <v>355</v>
+      </c>
+      <c r="O1" t="s">
+        <v>356</v>
+      </c>
+      <c r="P1" t="s">
         <v>357</v>
       </c>
-      <c r="L1" t="s">
+      <c r="Q1" t="s">
         <v>358</v>
-      </c>
-      <c r="M1" t="s">
-        <v>359</v>
-      </c>
-      <c r="N1" t="s">
-        <v>360</v>
-      </c>
-      <c r="O1" t="s">
-        <v>361</v>
-      </c>
-      <c r="P1" t="s">
-        <v>362</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -4499,7 +4440,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
@@ -4508,13 +4449,13 @@
         <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F2" s="1">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="G2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H2">
         <v>28.4</v>
@@ -4523,28 +4464,28 @@
         <v>27</v>
       </c>
       <c r="J2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K2" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M2" s="1">
         <v>46297</v>
       </c>
       <c r="N2" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="O2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="P2" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="Q2" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -4552,7 +4493,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -4561,19 +4502,19 @@
         <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F3" s="1">
         <v>46297</v>
       </c>
       <c r="G3" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="H3">
         <v>28.4</v>
       </c>
       <c r="I3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -4581,7 +4522,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
@@ -4590,13 +4531,13 @@
         <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F4" s="1">
-        <v>46300</v>
+        <v>46299</v>
       </c>
       <c r="G4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H4">
         <v>66.09999999999999</v>
@@ -4605,28 +4546,28 @@
         <v>28</v>
       </c>
       <c r="J4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K4" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L4" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M4" s="1">
         <v>46299</v>
       </c>
       <c r="N4" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="O4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="P4" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="Q4" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -4634,7 +4575,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
@@ -4643,19 +4584,19 @@
         <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F5" s="1">
         <v>46299</v>
       </c>
       <c r="G5" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="H5">
         <v>66.09999999999999</v>
       </c>
       <c r="I5" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -4663,7 +4604,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
@@ -4672,13 +4613,13 @@
         <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F6" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="G6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H6">
         <v>25.7</v>
@@ -4687,28 +4628,28 @@
         <v>29</v>
       </c>
       <c r="J6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K6" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L6" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M6" s="1">
         <v>46303</v>
       </c>
       <c r="N6" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="O6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="P6" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="Q6" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -4716,7 +4657,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
@@ -4725,19 +4666,19 @@
         <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F7" s="1">
         <v>46303</v>
       </c>
       <c r="G7" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H7">
         <v>25.7</v>
       </c>
       <c r="I7" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -4745,7 +4686,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -4754,13 +4695,13 @@
         <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F8" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="G8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H8">
         <v>74.5</v>
@@ -4769,28 +4710,28 @@
         <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K8" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L8" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M8" s="1">
         <v>46303</v>
       </c>
       <c r="N8" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="O8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="P8" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="Q8" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -4798,7 +4739,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
@@ -4807,19 +4748,19 @@
         <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F9" s="1">
         <v>46303</v>
       </c>
       <c r="G9" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="H9">
         <v>74.5</v>
       </c>
       <c r="I9" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -4827,7 +4768,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
@@ -4836,13 +4777,13 @@
         <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F10" s="1">
-        <v>46304</v>
+        <v>46303</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H10">
         <v>56.75</v>
@@ -4851,28 +4792,28 @@
         <v>31</v>
       </c>
       <c r="J10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K10" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L10" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M10" s="1">
         <v>46303</v>
       </c>
       <c r="N10" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="O10" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="P10" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="Q10" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -4880,7 +4821,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
@@ -4889,19 +4830,19 @@
         <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F11" s="1">
         <v>46303</v>
       </c>
       <c r="G11" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="H11">
         <v>56.75</v>
       </c>
       <c r="I11" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -4909,7 +4850,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
@@ -4918,13 +4859,13 @@
         <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F12" s="1">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="G12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H12">
         <v>37</v>
@@ -4933,28 +4874,28 @@
         <v>32</v>
       </c>
       <c r="J12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K12" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L12" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M12" s="1">
         <v>46306</v>
       </c>
       <c r="N12" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="O12" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="P12" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="Q12" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -4962,7 +4903,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
@@ -4971,19 +4912,19 @@
         <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F13" s="1">
         <v>46306</v>
       </c>
       <c r="G13" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="H13">
         <v>37</v>
       </c>
       <c r="I13" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -4991,7 +4932,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
@@ -5000,13 +4941,13 @@
         <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F14" s="1">
         <v>46308</v>
       </c>
       <c r="G14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H14">
         <v>47.9</v>
@@ -5015,28 +4956,28 @@
         <v>33</v>
       </c>
       <c r="J14" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="K14" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L14" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M14" s="1">
         <v>46308</v>
       </c>
       <c r="N14" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="O14" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="P14" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="Q14" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -5044,7 +4985,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
@@ -5053,19 +4994,19 @@
         <v>33</v>
       </c>
       <c r="E15" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F15" s="1">
         <v>46308</v>
       </c>
       <c r="G15" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="H15">
         <v>47.9</v>
       </c>
       <c r="I15" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -5073,7 +5014,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
@@ -5082,13 +5023,13 @@
         <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F16" s="1">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="G16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H16">
         <v>163.59</v>
@@ -5097,28 +5038,28 @@
         <v>34</v>
       </c>
       <c r="J16" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K16" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L16" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M16" s="1">
         <v>46299</v>
       </c>
       <c r="N16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O16" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="P16" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="Q16" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -5126,7 +5067,7 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C17" t="s">
         <v>15</v>
@@ -5135,19 +5076,19 @@
         <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F17" s="1">
         <v>46299</v>
       </c>
       <c r="G17" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="H17">
         <v>40.9</v>
       </c>
       <c r="I17" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -5155,7 +5096,7 @@
         <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C18" t="s">
         <v>15</v>
@@ -5164,19 +5105,19 @@
         <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F18" s="1">
         <v>46299</v>
       </c>
       <c r="G18" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="H18">
         <v>40.9</v>
       </c>
       <c r="I18" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -5184,7 +5125,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C19" t="s">
         <v>15</v>
@@ -5193,19 +5134,19 @@
         <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F19" s="1">
         <v>46299</v>
       </c>
       <c r="G19" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="H19">
         <v>81.79000000000001</v>
       </c>
       <c r="I19" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -5213,7 +5154,7 @@
         <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C20" t="s">
         <v>15</v>
@@ -5222,13 +5163,13 @@
         <v>35</v>
       </c>
       <c r="E20" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F20" s="1">
         <v>46300</v>
       </c>
       <c r="G20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H20">
         <v>74.90000000000001</v>
@@ -5237,28 +5178,28 @@
         <v>35</v>
       </c>
       <c r="J20" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K20" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L20" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M20" s="1">
         <v>46300</v>
       </c>
       <c r="N20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O20" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="P20" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="Q20" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -5266,7 +5207,7 @@
         <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C21" t="s">
         <v>15</v>
@@ -5275,19 +5216,19 @@
         <v>35</v>
       </c>
       <c r="E21" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F21" s="1">
         <v>46300</v>
       </c>
       <c r="G21" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="H21">
         <v>37.45</v>
       </c>
       <c r="I21" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
     </row>
     <row r="22" spans="1:17">
@@ -5295,7 +5236,7 @@
         <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C22" t="s">
         <v>15</v>
@@ -5304,19 +5245,19 @@
         <v>35</v>
       </c>
       <c r="E22" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F22" s="1">
         <v>46300</v>
       </c>
       <c r="G22" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="H22">
         <v>37.45</v>
       </c>
       <c r="I22" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
     </row>
     <row r="23" spans="1:17">
@@ -5324,7 +5265,7 @@
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C23" t="s">
         <v>15</v>
@@ -5333,13 +5274,13 @@
         <v>36</v>
       </c>
       <c r="E23" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F23" s="1">
         <v>46300</v>
       </c>
       <c r="G23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H23">
         <v>31.5</v>
@@ -5348,28 +5289,28 @@
         <v>36</v>
       </c>
       <c r="J23" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K23" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L23" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M23" s="1">
         <v>46300</v>
       </c>
       <c r="N23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O23" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="P23" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="Q23" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="24" spans="1:17">
@@ -5377,7 +5318,7 @@
         <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C24" t="s">
         <v>15</v>
@@ -5386,19 +5327,19 @@
         <v>36</v>
       </c>
       <c r="E24" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F24" s="1">
         <v>46300</v>
       </c>
       <c r="G24" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="H24">
         <v>31.5</v>
       </c>
       <c r="I24" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -5406,7 +5347,7 @@
         <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C25" t="s">
         <v>15</v>
@@ -5415,13 +5356,13 @@
         <v>37</v>
       </c>
       <c r="E25" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F25" s="1">
         <v>46304</v>
       </c>
       <c r="G25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H25">
         <v>101.9</v>
@@ -5430,28 +5371,28 @@
         <v>37</v>
       </c>
       <c r="J25" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K25" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L25" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M25" s="1">
         <v>46304</v>
       </c>
       <c r="N25" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="O25" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="P25" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="Q25" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="26" spans="1:17">
@@ -5459,7 +5400,7 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C26" t="s">
         <v>15</v>
@@ -5468,19 +5409,19 @@
         <v>37</v>
       </c>
       <c r="E26" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F26" s="1">
         <v>46304</v>
       </c>
       <c r="G26" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="H26">
         <v>101.9</v>
       </c>
       <c r="I26" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -5488,7 +5429,7 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C27" t="s">
         <v>15</v>
@@ -5497,13 +5438,13 @@
         <v>38</v>
       </c>
       <c r="E27" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F27" s="1">
         <v>46306</v>
       </c>
       <c r="G27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H27">
         <v>45.3</v>
@@ -5512,28 +5453,28 @@
         <v>38</v>
       </c>
       <c r="J27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K27" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L27" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M27" s="1">
         <v>46306</v>
       </c>
       <c r="N27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O27" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="P27" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="Q27" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -5541,7 +5482,7 @@
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C28" t="s">
         <v>15</v>
@@ -5550,19 +5491,19 @@
         <v>38</v>
       </c>
       <c r="E28" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F28" s="1">
         <v>46306</v>
       </c>
       <c r="G28" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="H28">
         <v>13.9</v>
       </c>
       <c r="I28" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -5570,7 +5511,7 @@
         <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C29" t="s">
         <v>15</v>
@@ -5579,19 +5520,19 @@
         <v>38</v>
       </c>
       <c r="E29" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F29" s="1">
         <v>46306</v>
       </c>
       <c r="G29" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="H29">
         <v>31.4</v>
       </c>
       <c r="I29" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -5599,7 +5540,7 @@
         <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C30" t="s">
         <v>15</v>
@@ -5608,13 +5549,13 @@
         <v>39</v>
       </c>
       <c r="E30" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F30" s="1">
         <v>46309</v>
       </c>
       <c r="G30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H30">
         <v>75.59999999999999</v>
@@ -5623,28 +5564,28 @@
         <v>39</v>
       </c>
       <c r="J30" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K30" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L30" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M30" s="1">
         <v>46309</v>
       </c>
       <c r="N30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O30" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="P30" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="Q30" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -5652,7 +5593,7 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C31" t="s">
         <v>15</v>
@@ -5661,19 +5602,19 @@
         <v>39</v>
       </c>
       <c r="E31" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F31" s="1">
         <v>46309</v>
       </c>
       <c r="G31" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="H31">
         <v>75.59999999999999</v>
       </c>
       <c r="I31" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -5681,7 +5622,7 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C32" t="s">
         <v>15</v>
@@ -5690,13 +5631,13 @@
         <v>40</v>
       </c>
       <c r="E32" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F32" s="1">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="G32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H32">
         <v>58.75</v>
@@ -5705,28 +5646,28 @@
         <v>40</v>
       </c>
       <c r="J32" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K32" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L32" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M32" s="1">
         <v>46298</v>
       </c>
       <c r="N32" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O32" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="P32" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="Q32" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -5734,7 +5675,7 @@
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C33" t="s">
         <v>15</v>
@@ -5743,19 +5684,19 @@
         <v>40</v>
       </c>
       <c r="E33" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F33" s="1">
         <v>46298</v>
       </c>
       <c r="G33" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="H33">
         <v>58.75</v>
       </c>
       <c r="I33" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="34" spans="1:17">
@@ -5763,7 +5704,7 @@
         <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C34" t="s">
         <v>15</v>
@@ -5772,13 +5713,13 @@
         <v>41</v>
       </c>
       <c r="E34" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F34" s="1">
         <v>46301</v>
       </c>
       <c r="G34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H34">
         <v>102.48</v>
@@ -5787,28 +5728,28 @@
         <v>41</v>
       </c>
       <c r="J34" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K34" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L34" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M34" s="1">
         <v>46301</v>
       </c>
       <c r="N34" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="O34" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="P34" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="Q34" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="35" spans="1:17">
@@ -5816,7 +5757,7 @@
         <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C35" t="s">
         <v>15</v>
@@ -5825,19 +5766,19 @@
         <v>41</v>
       </c>
       <c r="E35" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F35" s="1">
         <v>46301</v>
       </c>
       <c r="G35" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="H35">
         <v>42.48</v>
       </c>
       <c r="I35" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
     </row>
     <row r="36" spans="1:17">
@@ -5845,7 +5786,7 @@
         <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C36" t="s">
         <v>15</v>
@@ -5854,19 +5795,19 @@
         <v>41</v>
       </c>
       <c r="E36" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F36" s="1">
         <v>46301</v>
       </c>
       <c r="G36" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="H36">
         <v>60</v>
       </c>
       <c r="I36" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -5874,7 +5815,7 @@
         <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C37" t="s">
         <v>15</v>
@@ -5883,13 +5824,13 @@
         <v>42</v>
       </c>
       <c r="E37" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F37" s="1">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="G37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H37">
         <v>90</v>
@@ -5898,28 +5839,28 @@
         <v>42</v>
       </c>
       <c r="J37" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K37" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L37" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M37" s="1">
         <v>46304</v>
       </c>
       <c r="N37" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="O37" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="P37" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="Q37" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="38" spans="1:17">
@@ -5927,7 +5868,7 @@
         <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C38" t="s">
         <v>15</v>
@@ -5936,19 +5877,19 @@
         <v>42</v>
       </c>
       <c r="E38" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F38" s="1">
         <v>46304</v>
       </c>
       <c r="G38" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="H38">
         <v>90</v>
       </c>
       <c r="I38" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:17">
@@ -5956,7 +5897,7 @@
         <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C39" t="s">
         <v>15</v>
@@ -5965,13 +5906,13 @@
         <v>43</v>
       </c>
       <c r="E39" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F39" s="1">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="G39" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H39">
         <v>62.89</v>
@@ -5980,28 +5921,28 @@
         <v>43</v>
       </c>
       <c r="J39" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K39" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L39" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M39" s="1">
         <v>46307</v>
       </c>
       <c r="N39" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="O39" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="P39" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="Q39" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="40" spans="1:17">
@@ -6009,7 +5950,7 @@
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C40" t="s">
         <v>15</v>
@@ -6018,19 +5959,19 @@
         <v>43</v>
       </c>
       <c r="E40" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F40" s="1">
         <v>46307</v>
       </c>
       <c r="G40" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="H40">
         <v>62.89</v>
       </c>
       <c r="I40" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -6038,7 +5979,7 @@
         <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C41" t="s">
         <v>15</v>
@@ -6047,13 +5988,13 @@
         <v>44</v>
       </c>
       <c r="E41" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F41" s="1">
         <v>46309</v>
       </c>
       <c r="G41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H41">
         <v>20</v>
@@ -6062,28 +6003,28 @@
         <v>44</v>
       </c>
       <c r="J41" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K41" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L41" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M41" s="1">
         <v>46309</v>
       </c>
       <c r="N41" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="O41" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P41" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="Q41" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="42" spans="1:17">
@@ -6091,7 +6032,7 @@
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C42" t="s">
         <v>15</v>
@@ -6100,19 +6041,19 @@
         <v>44</v>
       </c>
       <c r="E42" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F42" s="1">
         <v>46309</v>
       </c>
       <c r="G42" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="H42">
         <v>20</v>
       </c>
       <c r="I42" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:17">
@@ -6120,7 +6061,7 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C43" t="s">
         <v>15</v>
@@ -6129,13 +6070,13 @@
         <v>45</v>
       </c>
       <c r="E43" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F43" s="1">
         <v>46298</v>
       </c>
       <c r="G43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H43">
         <v>31.5</v>
@@ -6144,28 +6085,28 @@
         <v>45</v>
       </c>
       <c r="J43" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K43" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L43" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M43" s="1">
         <v>46298</v>
       </c>
       <c r="N43" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="O43" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="P43" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="Q43" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="44" spans="1:17">
@@ -6173,7 +6114,7 @@
         <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C44" t="s">
         <v>15</v>
@@ -6182,19 +6123,19 @@
         <v>45</v>
       </c>
       <c r="E44" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F44" s="1">
         <v>46298</v>
       </c>
       <c r="G44" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="H44">
         <v>31.5</v>
       </c>
       <c r="I44" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:17">
@@ -6202,7 +6143,7 @@
         <v>13</v>
       </c>
       <c r="B45" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C45" t="s">
         <v>15</v>
@@ -6211,13 +6152,13 @@
         <v>46</v>
       </c>
       <c r="E45" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F45" s="1">
         <v>46300</v>
       </c>
       <c r="G45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H45">
         <v>44.8</v>
@@ -6226,28 +6167,28 @@
         <v>46</v>
       </c>
       <c r="J45" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K45" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L45" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M45" s="1">
         <v>46300</v>
       </c>
       <c r="N45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O45" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="P45" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="Q45" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="46" spans="1:17">
@@ -6255,7 +6196,7 @@
         <v>13</v>
       </c>
       <c r="B46" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C46" t="s">
         <v>15</v>
@@ -6264,19 +6205,19 @@
         <v>46</v>
       </c>
       <c r="E46" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F46" s="1">
         <v>46300</v>
       </c>
       <c r="G46" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="H46">
         <v>22.4</v>
       </c>
       <c r="I46" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
     </row>
     <row r="47" spans="1:17">
@@ -6284,7 +6225,7 @@
         <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C47" t="s">
         <v>15</v>
@@ -6293,19 +6234,19 @@
         <v>46</v>
       </c>
       <c r="E47" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F47" s="1">
         <v>46300</v>
       </c>
       <c r="G47" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="H47">
         <v>22.4</v>
       </c>
       <c r="I47" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="48" spans="1:17">
@@ -6313,7 +6254,7 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C48" t="s">
         <v>15</v>
@@ -6322,13 +6263,13 @@
         <v>47</v>
       </c>
       <c r="E48" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F48" s="1">
         <v>46303</v>
       </c>
       <c r="G48" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H48">
         <v>47.8</v>
@@ -6337,28 +6278,28 @@
         <v>47</v>
       </c>
       <c r="J48" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K48" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L48" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M48" s="1">
         <v>46303</v>
       </c>
       <c r="N48" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="O48" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="P48" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="Q48" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="49" spans="1:17">
@@ -6366,7 +6307,7 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C49" t="s">
         <v>15</v>
@@ -6375,19 +6316,19 @@
         <v>47</v>
       </c>
       <c r="E49" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F49" s="1">
         <v>46303</v>
       </c>
       <c r="G49" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H49">
         <v>47.8</v>
       </c>
       <c r="I49" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="50" spans="1:17">
@@ -6395,7 +6336,7 @@
         <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C50" t="s">
         <v>15</v>
@@ -6404,13 +6345,13 @@
         <v>48</v>
       </c>
       <c r="E50" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F50" s="1">
         <v>46303</v>
       </c>
       <c r="G50" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H50">
         <v>18.75</v>
@@ -6419,28 +6360,28 @@
         <v>48</v>
       </c>
       <c r="J50" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K50" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L50" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M50" s="1">
         <v>46303</v>
       </c>
       <c r="N50" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="O50" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="P50" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="Q50" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" spans="1:17">
@@ -6448,7 +6389,7 @@
         <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C51" t="s">
         <v>15</v>
@@ -6457,19 +6398,19 @@
         <v>48</v>
       </c>
       <c r="E51" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F51" s="1">
         <v>46303</v>
       </c>
       <c r="G51" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="H51">
         <v>18.75</v>
       </c>
       <c r="I51" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="52" spans="1:17">
@@ -6477,7 +6418,7 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C52" t="s">
         <v>16</v>
@@ -6486,13 +6427,13 @@
         <v>49</v>
       </c>
       <c r="E52" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F52" s="1">
         <v>46298</v>
       </c>
       <c r="G52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H52">
         <v>37.9</v>
@@ -6501,28 +6442,28 @@
         <v>49</v>
       </c>
       <c r="J52" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K52" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="L52" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M52" s="1">
         <v>46298</v>
       </c>
       <c r="N52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O52" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="P52" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="Q52" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="53" spans="1:17">
@@ -6530,7 +6471,7 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C53" t="s">
         <v>16</v>
@@ -6539,19 +6480,19 @@
         <v>49</v>
       </c>
       <c r="E53" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F53" s="1">
         <v>46298</v>
       </c>
       <c r="G53" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="H53">
         <v>37.9</v>
       </c>
       <c r="I53" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="54" spans="1:17">
@@ -6559,7 +6500,7 @@
         <v>13</v>
       </c>
       <c r="B54" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C54" t="s">
         <v>16</v>
@@ -6568,13 +6509,13 @@
         <v>50</v>
       </c>
       <c r="E54" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F54" s="1">
         <v>46301</v>
       </c>
       <c r="G54" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H54">
         <v>64.2</v>
@@ -6583,28 +6524,28 @@
         <v>50</v>
       </c>
       <c r="J54" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K54" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L54" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M54" s="1">
         <v>46301</v>
       </c>
       <c r="N54" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O54" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="P54" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="Q54" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="55" spans="1:17">
@@ -6612,7 +6553,7 @@
         <v>13</v>
       </c>
       <c r="B55" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C55" t="s">
         <v>16</v>
@@ -6621,19 +6562,19 @@
         <v>50</v>
       </c>
       <c r="E55" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F55" s="1">
         <v>46301</v>
       </c>
       <c r="G55" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="H55">
         <v>32.1</v>
       </c>
       <c r="I55" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
     </row>
     <row r="56" spans="1:17">
@@ -6641,7 +6582,7 @@
         <v>13</v>
       </c>
       <c r="B56" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C56" t="s">
         <v>16</v>
@@ -6650,19 +6591,19 @@
         <v>50</v>
       </c>
       <c r="E56" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F56" s="1">
         <v>46301</v>
       </c>
       <c r="G56" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="H56">
         <v>32.1</v>
       </c>
       <c r="I56" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="57" spans="1:17">
@@ -6670,7 +6611,7 @@
         <v>13</v>
       </c>
       <c r="B57" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C57" t="s">
         <v>16</v>
@@ -6679,13 +6620,13 @@
         <v>51</v>
       </c>
       <c r="E57" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F57" s="1">
         <v>46309</v>
       </c>
       <c r="G57" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H57">
         <v>49.8</v>
@@ -6694,28 +6635,28 @@
         <v>51</v>
       </c>
       <c r="J57" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K57" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L57" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M57" s="1">
         <v>46309</v>
       </c>
       <c r="N57" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="O57" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="P57" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="Q57" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="58" spans="1:17">
@@ -6723,7 +6664,7 @@
         <v>13</v>
       </c>
       <c r="B58" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C58" t="s">
         <v>16</v>
@@ -6732,19 +6673,19 @@
         <v>51</v>
       </c>
       <c r="E58" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F58" s="1">
         <v>46309</v>
       </c>
       <c r="G58" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H58">
         <v>20</v>
       </c>
       <c r="I58" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="59" spans="1:17">
@@ -6752,7 +6693,7 @@
         <v>13</v>
       </c>
       <c r="B59" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C59" t="s">
         <v>16</v>
@@ -6761,19 +6702,19 @@
         <v>51</v>
       </c>
       <c r="E59" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F59" s="1">
         <v>46309</v>
       </c>
       <c r="G59" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="H59">
         <v>29.8</v>
       </c>
       <c r="I59" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="60" spans="1:17">
@@ -6781,7 +6722,7 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C60" t="s">
         <v>17</v>
@@ -6790,13 +6731,13 @@
         <v>52</v>
       </c>
       <c r="E60" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F60" s="1">
-        <v>46303</v>
+        <v>46302</v>
       </c>
       <c r="G60" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H60">
         <v>68.3</v>
@@ -6805,28 +6746,28 @@
         <v>52</v>
       </c>
       <c r="J60" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K60" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L60" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M60" s="1">
         <v>46303</v>
       </c>
       <c r="N60" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="O60" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="P60" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="Q60" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="61" spans="1:17">
@@ -6834,7 +6775,7 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C61" t="s">
         <v>17</v>
@@ -6843,19 +6784,19 @@
         <v>52</v>
       </c>
       <c r="E61" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F61" s="1">
         <v>46303</v>
       </c>
       <c r="G61" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="H61">
         <v>68.3</v>
       </c>
       <c r="I61" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62" spans="1:17">
@@ -6863,7 +6804,7 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C62" t="s">
         <v>17</v>
@@ -6872,13 +6813,13 @@
         <v>53</v>
       </c>
       <c r="E62" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F62" s="1">
         <v>46296</v>
       </c>
       <c r="G62" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H62">
         <v>49.15</v>
@@ -6887,28 +6828,28 @@
         <v>53</v>
       </c>
       <c r="J62" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K62" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L62" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M62" s="1">
         <v>46296</v>
       </c>
       <c r="N62" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="O62" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="P62" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="Q62" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="63" spans="1:17">
@@ -6916,7 +6857,7 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C63" t="s">
         <v>17</v>
@@ -6925,19 +6866,19 @@
         <v>53</v>
       </c>
       <c r="E63" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F63" s="1">
         <v>46296</v>
       </c>
       <c r="G63" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="H63">
         <v>49.15</v>
       </c>
       <c r="I63" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="1:17">
@@ -6945,7 +6886,7 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C64" t="s">
         <v>18</v>
@@ -6954,13 +6895,13 @@
         <v>54</v>
       </c>
       <c r="E64" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F64" s="1">
         <v>46301</v>
       </c>
       <c r="G64" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H64">
         <v>89.67</v>
@@ -6969,28 +6910,28 @@
         <v>54</v>
       </c>
       <c r="J64" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K64" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L64" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M64" s="1">
         <v>46301</v>
       </c>
       <c r="N64" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O64" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="P64" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="Q64" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="65" spans="1:17">
@@ -6998,7 +6939,7 @@
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C65" t="s">
         <v>18</v>
@@ -7007,19 +6948,19 @@
         <v>54</v>
       </c>
       <c r="E65" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F65" s="1">
         <v>46301</v>
       </c>
       <c r="G65" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="H65">
         <v>89.67</v>
       </c>
       <c r="I65" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="1:17">
@@ -7027,7 +6968,7 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C66" t="s">
         <v>18</v>
@@ -7036,13 +6977,13 @@
         <v>55</v>
       </c>
       <c r="E66" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F66" s="1">
         <v>46303</v>
       </c>
       <c r="G66" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H66">
         <v>117.84</v>
@@ -7051,28 +6992,28 @@
         <v>55</v>
       </c>
       <c r="J66" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K66" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L66" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M66" s="1">
         <v>46303</v>
       </c>
       <c r="N66" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="O66" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="P66" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="Q66" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="67" spans="1:17">
@@ -7080,7 +7021,7 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C67" t="s">
         <v>18</v>
@@ -7089,19 +7030,19 @@
         <v>55</v>
       </c>
       <c r="E67" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F67" s="1">
         <v>46303</v>
       </c>
       <c r="G67" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="H67">
         <v>117.84</v>
       </c>
       <c r="I67" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="68" spans="1:17">
@@ -7109,7 +7050,7 @@
         <v>13</v>
       </c>
       <c r="B68" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C68" t="s">
         <v>18</v>
@@ -7118,13 +7059,13 @@
         <v>56</v>
       </c>
       <c r="E68" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F68" s="1">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="G68" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H68">
         <v>54.75</v>
@@ -7133,28 +7074,28 @@
         <v>56</v>
       </c>
       <c r="J68" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K68" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L68" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M68" s="1">
         <v>46305</v>
       </c>
       <c r="N68" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="O68" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="P68" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="Q68" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="69" spans="1:17">
@@ -7162,7 +7103,7 @@
         <v>13</v>
       </c>
       <c r="B69" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C69" t="s">
         <v>18</v>
@@ -7171,13 +7112,13 @@
         <v>56</v>
       </c>
       <c r="E69" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F69" s="1">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="G69" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H69">
         <v>7.5</v>
@@ -7186,28 +7127,28 @@
         <v>56</v>
       </c>
       <c r="J69" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K69" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L69" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M69" s="1">
         <v>46305</v>
       </c>
       <c r="N69" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="O69" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="P69" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="Q69" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="70" spans="1:17">
@@ -7215,7 +7156,7 @@
         <v>13</v>
       </c>
       <c r="B70" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C70" t="s">
         <v>18</v>
@@ -7224,19 +7165,19 @@
         <v>56</v>
       </c>
       <c r="E70" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F70" s="1">
         <v>46305</v>
       </c>
       <c r="G70" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H70">
         <v>62.25</v>
       </c>
       <c r="I70" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="71" spans="1:17">
@@ -7244,7 +7185,7 @@
         <v>13</v>
       </c>
       <c r="B71" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C71" t="s">
         <v>18</v>
@@ -7253,13 +7194,13 @@
         <v>57</v>
       </c>
       <c r="E71" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F71" s="1">
         <v>46296</v>
       </c>
       <c r="G71" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H71">
         <v>93.2</v>
@@ -7268,28 +7209,28 @@
         <v>57</v>
       </c>
       <c r="J71" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K71" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L71" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M71" s="1">
         <v>46296</v>
       </c>
       <c r="N71" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="O71" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="P71" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="Q71" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="72" spans="1:17">
@@ -7297,7 +7238,7 @@
         <v>13</v>
       </c>
       <c r="B72" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C72" t="s">
         <v>18</v>
@@ -7306,19 +7247,19 @@
         <v>57</v>
       </c>
       <c r="E72" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F72" s="1">
         <v>46296</v>
       </c>
       <c r="G72" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H72">
         <v>46.6</v>
       </c>
       <c r="I72" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
     </row>
     <row r="73" spans="1:17">
@@ -7326,7 +7267,7 @@
         <v>13</v>
       </c>
       <c r="B73" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C73" t="s">
         <v>18</v>
@@ -7335,19 +7276,19 @@
         <v>57</v>
       </c>
       <c r="E73" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F73" s="1">
         <v>46296</v>
       </c>
       <c r="G73" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="H73">
         <v>46.6</v>
       </c>
       <c r="I73" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="74" spans="1:17">
@@ -7355,7 +7296,7 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C74" t="s">
         <v>18</v>
@@ -7364,13 +7305,13 @@
         <v>58</v>
       </c>
       <c r="E74" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F74" s="1">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="G74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H74">
         <v>41</v>
@@ -7379,28 +7320,28 @@
         <v>58</v>
       </c>
       <c r="J74" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K74" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L74" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M74" s="1">
         <v>46308</v>
       </c>
       <c r="N74" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="O74" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="P74" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="Q74" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="75" spans="1:17">
@@ -7408,7 +7349,7 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C75" t="s">
         <v>18</v>
@@ -7417,19 +7358,19 @@
         <v>58</v>
       </c>
       <c r="E75" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F75" s="1">
         <v>46308</v>
       </c>
       <c r="G75" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H75">
         <v>41</v>
       </c>
       <c r="I75" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="76" spans="1:17">
@@ -7437,7 +7378,7 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C76" t="s">
         <v>18</v>
@@ -7446,13 +7387,13 @@
         <v>59</v>
       </c>
       <c r="E76" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F76" s="1">
-        <v>46298</v>
+        <v>46297</v>
       </c>
       <c r="G76" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H76">
         <v>27.5</v>
@@ -7461,28 +7402,28 @@
         <v>59</v>
       </c>
       <c r="J76" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K76" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L76" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M76" s="1">
         <v>46298</v>
       </c>
       <c r="N76" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="O76" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="P76" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="Q76" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="77" spans="1:17">
@@ -7490,7 +7431,7 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C77" t="s">
         <v>18</v>
@@ -7499,19 +7440,19 @@
         <v>59</v>
       </c>
       <c r="E77" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F77" s="1">
         <v>46298</v>
       </c>
       <c r="G77" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H77">
         <v>27.5</v>
       </c>
       <c r="I77" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="78" spans="1:17">
@@ -7519,7 +7460,7 @@
         <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C78" t="s">
         <v>18</v>
@@ -7528,13 +7469,13 @@
         <v>60</v>
       </c>
       <c r="E78" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F78" s="1">
         <v>46298</v>
       </c>
       <c r="G78" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H78">
         <v>64.3</v>
@@ -7543,28 +7484,28 @@
         <v>60</v>
       </c>
       <c r="J78" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K78" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="L78" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M78" s="1">
         <v>46298</v>
       </c>
       <c r="N78" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="O78" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="P78" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="Q78" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="79" spans="1:17">
@@ -7572,7 +7513,7 @@
         <v>13</v>
       </c>
       <c r="B79" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C79" t="s">
         <v>18</v>
@@ -7581,13 +7522,13 @@
         <v>60</v>
       </c>
       <c r="E79" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F79" s="1">
         <v>46298</v>
       </c>
       <c r="G79" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H79">
         <v>6</v>
@@ -7596,28 +7537,28 @@
         <v>60</v>
       </c>
       <c r="J79" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K79" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L79" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M79" s="1">
         <v>46298</v>
       </c>
       <c r="N79" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="O79" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="P79" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="Q79" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="80" spans="1:17">
@@ -7625,7 +7566,7 @@
         <v>13</v>
       </c>
       <c r="B80" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C80" t="s">
         <v>18</v>
@@ -7634,19 +7575,19 @@
         <v>60</v>
       </c>
       <c r="E80" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F80" s="1">
         <v>46298</v>
       </c>
       <c r="G80" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="H80">
         <v>70.3</v>
       </c>
       <c r="I80" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="81" spans="1:17">
@@ -7654,7 +7595,7 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C81" t="s">
         <v>19</v>
@@ -7663,13 +7604,13 @@
         <v>61</v>
       </c>
       <c r="E81" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F81" s="1">
         <v>46301</v>
       </c>
       <c r="G81" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H81">
         <v>16.75</v>
@@ -7678,28 +7619,28 @@
         <v>61</v>
       </c>
       <c r="J81" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K81" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="L81" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M81" s="1">
         <v>46301</v>
       </c>
       <c r="N81" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="O81" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="P81" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="Q81" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="82" spans="1:17">
@@ -7707,7 +7648,7 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C82" t="s">
         <v>19</v>
@@ -7716,19 +7657,19 @@
         <v>61</v>
       </c>
       <c r="E82" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F82" s="1">
         <v>46301</v>
       </c>
       <c r="G82" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="H82">
         <v>16.75</v>
       </c>
       <c r="I82" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="83" spans="1:17">
@@ -7736,7 +7677,7 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C83" t="s">
         <v>20</v>
@@ -7745,13 +7686,13 @@
         <v>62</v>
       </c>
       <c r="E83" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F83" s="1">
         <v>46300</v>
       </c>
       <c r="G83" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H83">
         <v>74.8</v>
@@ -7760,28 +7701,28 @@
         <v>62</v>
       </c>
       <c r="J83" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K83" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L83" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M83" s="1">
         <v>46300</v>
       </c>
       <c r="N83" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="O83" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="P83" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="Q83" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="84" spans="1:17">
@@ -7789,7 +7730,7 @@
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C84" t="s">
         <v>20</v>
@@ -7798,19 +7739,19 @@
         <v>62</v>
       </c>
       <c r="E84" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F84" s="1">
         <v>46300</v>
       </c>
       <c r="G84" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H84">
         <v>74.8</v>
       </c>
       <c r="I84" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="85" spans="1:17">
@@ -7818,7 +7759,7 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C85" t="s">
         <v>20</v>
@@ -7827,13 +7768,13 @@
         <v>63</v>
       </c>
       <c r="E85" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F85" s="1">
         <v>46300</v>
       </c>
       <c r="G85" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H85">
         <v>58.2</v>
@@ -7842,28 +7783,28 @@
         <v>63</v>
       </c>
       <c r="J85" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K85" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L85" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M85" s="1">
         <v>46300</v>
       </c>
       <c r="N85" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="O85" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="P85" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="Q85" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="86" spans="1:17">
@@ -7871,7 +7812,7 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C86" t="s">
         <v>20</v>
@@ -7880,19 +7821,19 @@
         <v>63</v>
       </c>
       <c r="E86" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F86" s="1">
         <v>46300</v>
       </c>
       <c r="G86" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="H86">
         <v>58.2</v>
       </c>
       <c r="I86" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="87" spans="1:17">
@@ -7900,7 +7841,7 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C87" t="s">
         <v>20</v>
@@ -7909,13 +7850,13 @@
         <v>64</v>
       </c>
       <c r="E87" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F87" s="1">
         <v>46300</v>
       </c>
       <c r="G87" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H87">
         <v>39</v>
@@ -7924,28 +7865,28 @@
         <v>64</v>
       </c>
       <c r="J87" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K87" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L87" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M87" s="1">
         <v>46300</v>
       </c>
       <c r="N87" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="O87" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="P87" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="Q87" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="88" spans="1:17">
@@ -7953,7 +7894,7 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C88" t="s">
         <v>20</v>
@@ -7962,19 +7903,19 @@
         <v>64</v>
       </c>
       <c r="E88" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F88" s="1">
         <v>46300</v>
       </c>
       <c r="G88" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="H88">
         <v>39</v>
       </c>
       <c r="I88" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="89" spans="1:17">
@@ -7982,7 +7923,7 @@
         <v>13</v>
       </c>
       <c r="B89" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C89" t="s">
         <v>20</v>
@@ -7991,13 +7932,13 @@
         <v>65</v>
       </c>
       <c r="E89" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F89" s="1">
         <v>46300</v>
       </c>
       <c r="G89" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H89">
         <v>16.6</v>
@@ -8006,28 +7947,28 @@
         <v>65</v>
       </c>
       <c r="J89" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K89" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L89" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M89" s="1">
         <v>46300</v>
       </c>
       <c r="N89" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="O89" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="P89" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="Q89" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="90" spans="1:17">
@@ -8035,7 +7976,7 @@
         <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C90" t="s">
         <v>20</v>
@@ -8044,13 +7985,13 @@
         <v>65</v>
       </c>
       <c r="E90" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F90" s="1">
         <v>46300</v>
       </c>
       <c r="G90" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H90">
         <v>56.6</v>
@@ -8059,28 +8000,28 @@
         <v>65</v>
       </c>
       <c r="J90" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K90" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L90" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M90" s="1">
         <v>46300</v>
       </c>
       <c r="N90" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="O90" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="P90" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="Q90" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="91" spans="1:17">
@@ -8088,7 +8029,7 @@
         <v>13</v>
       </c>
       <c r="B91" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C91" t="s">
         <v>20</v>
@@ -8097,19 +8038,19 @@
         <v>65</v>
       </c>
       <c r="E91" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F91" s="1">
         <v>46300</v>
       </c>
       <c r="G91" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="H91">
         <v>73.2</v>
       </c>
       <c r="I91" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="92" spans="1:17">
@@ -8117,7 +8058,7 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C92" t="s">
         <v>20</v>
@@ -8126,13 +8067,13 @@
         <v>66</v>
       </c>
       <c r="E92" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F92" s="1">
-        <v>46305</v>
+        <v>46304</v>
       </c>
       <c r="G92" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H92">
         <v>75.3</v>
@@ -8141,28 +8082,28 @@
         <v>66</v>
       </c>
       <c r="J92" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K92" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L92" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M92" s="1">
         <v>46305</v>
       </c>
       <c r="N92" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="O92" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="P92" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="Q92" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="93" spans="1:17">
@@ -8170,7 +8111,7 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C93" t="s">
         <v>20</v>
@@ -8179,19 +8120,19 @@
         <v>66</v>
       </c>
       <c r="E93" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F93" s="1">
         <v>46305</v>
       </c>
       <c r="G93" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="H93">
         <v>75.3</v>
       </c>
       <c r="I93" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="94" spans="1:17">
@@ -8199,7 +8140,7 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C94" t="s">
         <v>20</v>
@@ -8208,13 +8149,13 @@
         <v>67</v>
       </c>
       <c r="E94" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F94" s="1">
         <v>46305</v>
       </c>
       <c r="G94" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H94">
         <v>7.9</v>
@@ -8223,28 +8164,28 @@
         <v>67</v>
       </c>
       <c r="J94" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K94" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L94" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M94" s="1">
         <v>46305</v>
       </c>
       <c r="N94" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="O94" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="P94" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="Q94" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="95" spans="1:17">
@@ -8252,7 +8193,7 @@
         <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C95" t="s">
         <v>20</v>
@@ -8261,19 +8202,19 @@
         <v>67</v>
       </c>
       <c r="E95" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F95" s="1">
         <v>46305</v>
       </c>
       <c r="G95" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H95">
         <v>7.9</v>
       </c>
       <c r="I95" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="96" spans="1:17">
@@ -8281,7 +8222,7 @@
         <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C96" t="s">
         <v>20</v>
@@ -8290,13 +8231,13 @@
         <v>68</v>
       </c>
       <c r="E96" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F96" s="1">
         <v>46306</v>
       </c>
       <c r="G96" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H96">
         <v>50</v>
@@ -8305,28 +8246,28 @@
         <v>68</v>
       </c>
       <c r="J96" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K96" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L96" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M96" s="1">
         <v>46306</v>
       </c>
       <c r="N96" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="O96" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="P96" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="Q96" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="97" spans="1:17">
@@ -8334,7 +8275,7 @@
         <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C97" t="s">
         <v>20</v>
@@ -8343,19 +8284,19 @@
         <v>68</v>
       </c>
       <c r="E97" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F97" s="1">
         <v>46306</v>
       </c>
       <c r="G97" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="H97">
         <v>20</v>
       </c>
       <c r="I97" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="98" spans="1:17">
@@ -8363,7 +8304,7 @@
         <v>13</v>
       </c>
       <c r="B98" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C98" t="s">
         <v>20</v>
@@ -8372,19 +8313,19 @@
         <v>68</v>
       </c>
       <c r="E98" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F98" s="1">
         <v>46306</v>
       </c>
       <c r="G98" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="H98">
         <v>30</v>
       </c>
       <c r="I98" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
     </row>
     <row r="99" spans="1:17">
@@ -8392,7 +8333,7 @@
         <v>13</v>
       </c>
       <c r="B99" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C99" t="s">
         <v>20</v>
@@ -8401,13 +8342,13 @@
         <v>69</v>
       </c>
       <c r="E99" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F99" s="1">
         <v>46307</v>
       </c>
       <c r="G99" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H99">
         <v>38</v>
@@ -8416,28 +8357,28 @@
         <v>69</v>
       </c>
       <c r="J99" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K99" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L99" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M99" s="1">
         <v>46307</v>
       </c>
       <c r="N99" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O99" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="P99" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="Q99" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="100" spans="1:17">
@@ -8445,7 +8386,7 @@
         <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C100" t="s">
         <v>20</v>
@@ -8454,19 +8395,19 @@
         <v>69</v>
       </c>
       <c r="E100" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F100" s="1">
         <v>46307</v>
       </c>
       <c r="G100" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="H100">
         <v>18</v>
       </c>
       <c r="I100" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="101" spans="1:17">
@@ -8474,7 +8415,7 @@
         <v>13</v>
       </c>
       <c r="B101" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C101" t="s">
         <v>20</v>
@@ -8483,19 +8424,19 @@
         <v>69</v>
       </c>
       <c r="E101" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F101" s="1">
         <v>46307</v>
       </c>
       <c r="G101" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H101">
         <v>20</v>
       </c>
       <c r="I101" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
     </row>
     <row r="102" spans="1:17">
@@ -8503,7 +8444,7 @@
         <v>13</v>
       </c>
       <c r="B102" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C102" t="s">
         <v>20</v>
@@ -8512,13 +8453,13 @@
         <v>70</v>
       </c>
       <c r="E102" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F102" s="1">
         <v>46296</v>
       </c>
       <c r="G102" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H102">
         <v>50.25</v>
@@ -8527,28 +8468,28 @@
         <v>70</v>
       </c>
       <c r="J102" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K102" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="L102" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M102" s="1">
         <v>46296</v>
       </c>
       <c r="N102" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="O102" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="P102" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="Q102" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="103" spans="1:17">
@@ -8556,7 +8497,7 @@
         <v>13</v>
       </c>
       <c r="B103" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C103" t="s">
         <v>20</v>
@@ -8565,19 +8506,19 @@
         <v>70</v>
       </c>
       <c r="E103" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F103" s="1">
         <v>46296</v>
       </c>
       <c r="G103" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="H103">
         <v>36.5</v>
       </c>
       <c r="I103" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="104" spans="1:17">
@@ -8585,7 +8526,7 @@
         <v>13</v>
       </c>
       <c r="B104" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C104" t="s">
         <v>20</v>
@@ -8594,19 +8535,19 @@
         <v>70</v>
       </c>
       <c r="E104" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F104" s="1">
         <v>46296</v>
       </c>
       <c r="G104" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="H104">
         <v>13.75</v>
       </c>
       <c r="I104" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
     </row>
     <row r="105" spans="1:17">
@@ -8614,7 +8555,7 @@
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C105" t="s">
         <v>20</v>
@@ -8623,13 +8564,13 @@
         <v>71</v>
       </c>
       <c r="E105" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F105" s="1">
         <v>46305</v>
       </c>
       <c r="G105" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H105">
         <v>9.220000000000001</v>
@@ -8638,28 +8579,28 @@
         <v>71</v>
       </c>
       <c r="J105" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K105" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="L105" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M105" s="1">
         <v>46305</v>
       </c>
       <c r="N105" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O105" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="P105" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="Q105" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="106" spans="1:17">
@@ -8667,7 +8608,7 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C106" t="s">
         <v>20</v>
@@ -8676,19 +8617,19 @@
         <v>71</v>
       </c>
       <c r="E106" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F106" s="1">
         <v>46305</v>
       </c>
       <c r="G106" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="H106">
         <v>9.220000000000001</v>
       </c>
       <c r="I106" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="107" spans="1:17">
@@ -8696,7 +8637,7 @@
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C107" t="s">
         <v>20</v>
@@ -8705,13 +8646,13 @@
         <v>72</v>
       </c>
       <c r="E107" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F107" s="1">
         <v>46297</v>
       </c>
       <c r="G107" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H107">
         <v>54.05</v>
@@ -8720,28 +8661,28 @@
         <v>72</v>
       </c>
       <c r="J107" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K107" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L107" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M107" s="1">
         <v>46297</v>
       </c>
       <c r="N107" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="O107" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="P107" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="Q107" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="108" spans="1:17">
@@ -8749,7 +8690,7 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C108" t="s">
         <v>20</v>
@@ -8758,19 +8699,19 @@
         <v>72</v>
       </c>
       <c r="E108" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F108" s="1">
         <v>46297</v>
       </c>
       <c r="G108" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="H108">
         <v>54.05</v>
       </c>
       <c r="I108" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="109" spans="1:17">
@@ -8778,7 +8719,7 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C109" t="s">
         <v>20</v>
@@ -8787,13 +8728,13 @@
         <v>73</v>
       </c>
       <c r="E109" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F109" s="1">
         <v>46297</v>
       </c>
       <c r="G109" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H109">
         <v>20.25</v>
@@ -8802,28 +8743,28 @@
         <v>73</v>
       </c>
       <c r="J109" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K109" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L109" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M109" s="1">
         <v>46297</v>
       </c>
       <c r="N109" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="O109" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="P109" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="Q109" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="110" spans="1:17">
@@ -8831,7 +8772,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C110" t="s">
         <v>20</v>
@@ -8840,19 +8781,19 @@
         <v>73</v>
       </c>
       <c r="E110" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F110" s="1">
         <v>46297</v>
       </c>
       <c r="G110" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="H110">
         <v>20.25</v>
       </c>
       <c r="I110" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="111" spans="1:17">
@@ -8860,7 +8801,7 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C111" t="s">
         <v>20</v>
@@ -8869,13 +8810,13 @@
         <v>74</v>
       </c>
       <c r="E111" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F111" s="1">
         <v>46297</v>
       </c>
       <c r="G111" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H111">
         <v>54.3</v>
@@ -8884,28 +8825,28 @@
         <v>74</v>
       </c>
       <c r="J111" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K111" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L111" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="M111" s="1">
         <v>46297</v>
       </c>
       <c r="N111" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="O111" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="P111" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="Q111" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="112" spans="1:17">
@@ -8913,7 +8854,7 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C112" t="s">
         <v>20</v>
@@ -8922,19 +8863,19 @@
         <v>74</v>
       </c>
       <c r="E112" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F112" s="1">
         <v>46297</v>
       </c>
       <c r="G112" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="H112">
         <v>54.3</v>
       </c>
       <c r="I112" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="113" spans="1:17">
@@ -8942,7 +8883,7 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C113" t="s">
         <v>21</v>
@@ -8951,13 +8892,13 @@
         <v>75</v>
       </c>
       <c r="E113" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F113" s="1">
         <v>46305</v>
       </c>
       <c r="G113" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H113">
         <v>70.40000000000001</v>
@@ -8966,28 +8907,28 @@
         <v>75</v>
       </c>
       <c r="J113" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K113" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L113" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M113" s="1">
         <v>46305</v>
       </c>
       <c r="N113" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="O113" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="P113" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="Q113" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="114" spans="1:17">
@@ -8995,7 +8936,7 @@
         <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C114" t="s">
         <v>21</v>
@@ -9004,19 +8945,19 @@
         <v>75</v>
       </c>
       <c r="E114" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F114" s="1">
         <v>46305</v>
       </c>
       <c r="G114" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="H114">
         <v>70.40000000000001</v>
       </c>
       <c r="I114" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="115" spans="1:17">
@@ -9024,7 +8965,7 @@
         <v>13</v>
       </c>
       <c r="B115" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C115" t="s">
         <v>21</v>
@@ -9033,13 +8974,13 @@
         <v>76</v>
       </c>
       <c r="E115" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F115" s="1">
-        <v>46306</v>
+        <v>46305</v>
       </c>
       <c r="G115" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H115">
         <v>47.25</v>
@@ -9048,28 +8989,28 @@
         <v>76</v>
       </c>
       <c r="J115" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K115" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L115" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M115" s="1">
         <v>46306</v>
       </c>
       <c r="N115" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="O115" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="P115" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="Q115" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="116" spans="1:17">
@@ -9077,7 +9018,7 @@
         <v>13</v>
       </c>
       <c r="B116" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C116" t="s">
         <v>21</v>
@@ -9086,19 +9027,19 @@
         <v>76</v>
       </c>
       <c r="E116" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F116" s="1">
         <v>46306</v>
       </c>
       <c r="G116" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="H116">
         <v>15.75</v>
       </c>
       <c r="I116" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
     </row>
     <row r="117" spans="1:17">
@@ -9106,7 +9047,7 @@
         <v>13</v>
       </c>
       <c r="B117" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C117" t="s">
         <v>21</v>
@@ -9115,19 +9056,19 @@
         <v>76</v>
       </c>
       <c r="E117" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F117" s="1">
         <v>46306</v>
       </c>
       <c r="G117" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="H117">
         <v>15.75</v>
       </c>
       <c r="I117" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
     <row r="118" spans="1:17">
@@ -9135,7 +9076,7 @@
         <v>13</v>
       </c>
       <c r="B118" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C118" t="s">
         <v>21</v>
@@ -9144,19 +9085,19 @@
         <v>76</v>
       </c>
       <c r="E118" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F118" s="1">
         <v>46306</v>
       </c>
       <c r="G118" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="H118">
         <v>15.75</v>
       </c>
       <c r="I118" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
     <row r="119" spans="1:17">
@@ -9164,7 +9105,7 @@
         <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C119" t="s">
         <v>22</v>
@@ -9173,43 +9114,43 @@
         <v>77</v>
       </c>
       <c r="E119" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F119" s="1">
-        <v>46301</v>
+        <v>46305</v>
       </c>
       <c r="G119" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H119">
-        <v>52.4</v>
+        <v>14.9</v>
       </c>
       <c r="I119" t="s">
         <v>77</v>
       </c>
       <c r="J119" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="K119" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="L119" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="M119" s="1">
-        <v>46302</v>
+        <v>46305</v>
       </c>
       <c r="N119" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="O119" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="P119" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="Q119" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
     </row>
     <row r="120" spans="1:17">
@@ -9217,7 +9158,7 @@
         <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C120" t="s">
         <v>22</v>
@@ -9226,27 +9167,27 @@
         <v>77</v>
       </c>
       <c r="E120" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F120" s="1">
-        <v>46302</v>
+        <v>46305</v>
       </c>
       <c r="G120" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="H120">
-        <v>52.4</v>
+        <v>14.9</v>
       </c>
       <c r="I120" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="121" spans="1:17">
       <c r="A121" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B121" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C121" t="s">
         <v>22</v>
@@ -9255,51 +9196,51 @@
         <v>78</v>
       </c>
       <c r="E121" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F121" s="1">
-        <v>46305</v>
+        <v>46298</v>
       </c>
       <c r="G121" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H121">
-        <v>14.9</v>
+        <v>86.18000000000001</v>
       </c>
       <c r="I121" t="s">
         <v>78</v>
       </c>
       <c r="J121" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K121" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L121" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="M121" s="1">
-        <v>46305</v>
+        <v>46298</v>
       </c>
       <c r="N121" t="s">
-        <v>525</v>
+        <v>134</v>
       </c>
       <c r="O121" t="s">
-        <v>343</v>
+        <v>468</v>
       </c>
       <c r="P121" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="Q121" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="122" spans="1:17">
       <c r="A122" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B122" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C122" t="s">
         <v>22</v>
@@ -9308,19 +9249,19 @@
         <v>78</v>
       </c>
       <c r="E122" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F122" s="1">
-        <v>46305</v>
+        <v>46298</v>
       </c>
       <c r="G122" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="H122">
-        <v>14.9</v>
+        <v>43.09</v>
       </c>
       <c r="I122" t="s">
-        <v>343</v>
+        <v>468</v>
       </c>
     </row>
     <row r="123" spans="1:17">
@@ -9328,110 +9269,110 @@
         <v>13</v>
       </c>
       <c r="B123" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C123" t="s">
         <v>22</v>
       </c>
       <c r="D123" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E123" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F123" s="1">
         <v>46298</v>
       </c>
       <c r="G123" t="s">
-        <v>136</v>
+        <v>430</v>
       </c>
       <c r="H123">
-        <v>86.18000000000001</v>
+        <v>43.09</v>
       </c>
       <c r="I123" t="s">
-        <v>79</v>
-      </c>
-      <c r="J123" t="s">
-        <v>163</v>
-      </c>
-      <c r="K123" t="s">
-        <v>483</v>
-      </c>
-      <c r="L123" t="s">
-        <v>366</v>
-      </c>
-      <c r="M123" s="1">
-        <v>46298</v>
-      </c>
-      <c r="N123" t="s">
-        <v>136</v>
-      </c>
-      <c r="O123" t="s">
-        <v>474</v>
-      </c>
-      <c r="P123" t="s">
-        <v>562</v>
-      </c>
-      <c r="Q123" t="s">
-        <v>572</v>
+        <v>469</v>
       </c>
     </row>
     <row r="124" spans="1:17">
       <c r="A124" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C124" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D124" t="s">
         <v>79</v>
       </c>
       <c r="E124" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F124" s="1">
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="G124" t="s">
-        <v>435</v>
+        <v>135</v>
       </c>
       <c r="H124">
-        <v>43.09</v>
+        <v>23.65</v>
       </c>
       <c r="I124" t="s">
-        <v>474</v>
+        <v>79</v>
+      </c>
+      <c r="J124" t="s">
+        <v>162</v>
+      </c>
+      <c r="K124" t="s">
+        <v>476</v>
+      </c>
+      <c r="L124" t="s">
+        <v>363</v>
+      </c>
+      <c r="M124" s="1">
+        <v>46302</v>
+      </c>
+      <c r="N124" t="s">
+        <v>135</v>
+      </c>
+      <c r="O124" t="s">
+        <v>340</v>
+      </c>
+      <c r="P124" t="s">
+        <v>556</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="125" spans="1:17">
       <c r="A125" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C125" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D125" t="s">
         <v>79</v>
       </c>
       <c r="E125" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="F125" s="1">
-        <v>46298</v>
+        <v>46302</v>
       </c>
       <c r="G125" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="H125">
-        <v>43.09</v>
+        <v>23.65</v>
       </c>
       <c r="I125" t="s">
-        <v>475</v>
+        <v>340</v>
       </c>
     </row>
     <row r="126" spans="1:17">
@@ -9439,7 +9380,7 @@
         <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C126" t="s">
         <v>23</v>
@@ -9448,43 +9389,43 @@
         <v>80</v>
       </c>
       <c r="E126" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F126" s="1">
-        <v>46302</v>
+        <v>46296</v>
       </c>
       <c r="G126" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="H126">
-        <v>23.65</v>
+        <v>33</v>
       </c>
       <c r="I126" t="s">
         <v>80</v>
       </c>
       <c r="J126" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K126" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L126" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M126" s="1">
-        <v>46302</v>
+        <v>46297</v>
       </c>
       <c r="N126" t="s">
-        <v>137</v>
+        <v>520</v>
       </c>
       <c r="O126" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="P126" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="Q126" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="127" spans="1:17">
@@ -9492,7 +9433,7 @@
         <v>12</v>
       </c>
       <c r="B127" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C127" t="s">
         <v>23</v>
@@ -9501,19 +9442,19 @@
         <v>80</v>
       </c>
       <c r="E127" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F127" s="1">
-        <v>46302</v>
+        <v>46297</v>
       </c>
       <c r="G127" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="H127">
-        <v>23.65</v>
+        <v>33</v>
       </c>
       <c r="I127" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="128" spans="1:17">
@@ -9521,7 +9462,7 @@
         <v>12</v>
       </c>
       <c r="B128" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C128" t="s">
         <v>23</v>
@@ -9530,43 +9471,43 @@
         <v>81</v>
       </c>
       <c r="E128" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F128" s="1">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="G128" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="H128">
-        <v>33</v>
+        <v>42.6</v>
       </c>
       <c r="I128" t="s">
         <v>81</v>
       </c>
       <c r="J128" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K128" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="L128" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="M128" s="1">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="N128" t="s">
-        <v>526</v>
+        <v>136</v>
       </c>
       <c r="O128" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="P128" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="Q128" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="129" spans="1:17">
@@ -9574,7 +9515,7 @@
         <v>12</v>
       </c>
       <c r="B129" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C129" t="s">
         <v>23</v>
@@ -9583,19 +9524,19 @@
         <v>81</v>
       </c>
       <c r="E129" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F129" s="1">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="G129" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="H129">
-        <v>33</v>
+        <v>42.6</v>
       </c>
       <c r="I129" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="130" spans="1:17">
@@ -9603,7 +9544,7 @@
         <v>12</v>
       </c>
       <c r="B130" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C130" t="s">
         <v>23</v>
@@ -9612,43 +9553,43 @@
         <v>82</v>
       </c>
       <c r="E130" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F130" s="1">
-        <v>46296</v>
+        <v>46302</v>
       </c>
       <c r="G130" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H130">
-        <v>42.6</v>
+        <v>9.9</v>
       </c>
       <c r="I130" t="s">
         <v>82</v>
       </c>
       <c r="J130" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="K130" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="L130" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="M130" s="1">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="N130" t="s">
-        <v>138</v>
+        <v>521</v>
       </c>
       <c r="O130" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="P130" t="s">
+        <v>558</v>
+      </c>
+      <c r="Q130" t="s">
         <v>563</v>
-      </c>
-      <c r="Q130" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="131" spans="1:17">
@@ -9656,7 +9597,7 @@
         <v>12</v>
       </c>
       <c r="B131" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C131" t="s">
         <v>23</v>
@@ -9665,101 +9606,101 @@
         <v>82</v>
       </c>
       <c r="E131" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F131" s="1">
-        <v>46296</v>
+        <v>46301</v>
       </c>
       <c r="G131" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="H131">
-        <v>42.6</v>
+        <v>9.9</v>
       </c>
       <c r="I131" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="132" spans="1:17">
       <c r="A132" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B132" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C132" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D132" t="s">
         <v>83</v>
       </c>
       <c r="E132" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F132" s="1">
-        <v>46302</v>
+        <v>46296</v>
       </c>
       <c r="G132" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H132">
-        <v>9.9</v>
+        <v>45.3</v>
       </c>
       <c r="I132" t="s">
         <v>83</v>
       </c>
       <c r="J132" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K132" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="L132" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="M132" s="1">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="N132" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="O132" t="s">
-        <v>348</v>
+        <v>470</v>
       </c>
       <c r="P132" t="s">
+        <v>559</v>
+      </c>
+      <c r="Q132" t="s">
         <v>565</v>
-      </c>
-      <c r="Q132" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="133" spans="1:17">
       <c r="A133" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B133" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C133" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D133" t="s">
         <v>83</v>
       </c>
       <c r="E133" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F133" s="1">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="G133" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="H133">
-        <v>9.9</v>
+        <v>22.65</v>
       </c>
       <c r="I133" t="s">
-        <v>348</v>
+        <v>470</v>
       </c>
     </row>
     <row r="134" spans="1:17">
@@ -9767,52 +9708,28 @@
         <v>13</v>
       </c>
       <c r="B134" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C134" t="s">
         <v>24</v>
       </c>
       <c r="D134" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E134" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F134" s="1">
         <v>46296</v>
       </c>
       <c r="G134" t="s">
-        <v>140</v>
+        <v>436</v>
       </c>
       <c r="H134">
-        <v>45.3</v>
+        <v>22.65</v>
       </c>
       <c r="I134" t="s">
-        <v>84</v>
-      </c>
-      <c r="J134" t="s">
-        <v>167</v>
-      </c>
-      <c r="K134" t="s">
-        <v>483</v>
-      </c>
-      <c r="L134" t="s">
-        <v>367</v>
-      </c>
-      <c r="M134" s="1">
-        <v>46296</v>
-      </c>
-      <c r="N134" t="s">
-        <v>528</v>
-      </c>
-      <c r="O134" t="s">
-        <v>476</v>
-      </c>
-      <c r="P134" t="s">
-        <v>566</v>
-      </c>
-      <c r="Q134" t="s">
-        <v>572</v>
+        <v>471</v>
       </c>
     </row>
     <row r="135" spans="1:17">
@@ -9820,28 +9737,52 @@
         <v>13</v>
       </c>
       <c r="B135" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C135" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D135" t="s">
         <v>84</v>
       </c>
       <c r="E135" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F135" s="1">
-        <v>46296</v>
+        <v>46304</v>
       </c>
       <c r="G135" t="s">
-        <v>441</v>
+        <v>139</v>
       </c>
       <c r="H135">
-        <v>22.65</v>
+        <v>46</v>
       </c>
       <c r="I135" t="s">
+        <v>84</v>
+      </c>
+      <c r="J135" t="s">
+        <v>166</v>
+      </c>
+      <c r="K135" t="s">
         <v>476</v>
+      </c>
+      <c r="L135" t="s">
+        <v>361</v>
+      </c>
+      <c r="M135" s="1">
+        <v>46304</v>
+      </c>
+      <c r="N135" t="s">
+        <v>523</v>
+      </c>
+      <c r="O135" t="s">
+        <v>472</v>
+      </c>
+      <c r="P135" t="s">
+        <v>560</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="136" spans="1:17">
@@ -9849,28 +9790,28 @@
         <v>13</v>
       </c>
       <c r="B136" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C136" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D136" t="s">
         <v>84</v>
       </c>
       <c r="E136" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F136" s="1">
-        <v>46296</v>
+        <v>46304</v>
       </c>
       <c r="G136" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="H136">
-        <v>22.65</v>
+        <v>23</v>
       </c>
       <c r="I136" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="137" spans="1:17">
@@ -9878,52 +9819,28 @@
         <v>13</v>
       </c>
       <c r="B137" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C137" t="s">
         <v>25</v>
       </c>
       <c r="D137" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E137" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F137" s="1">
         <v>46304</v>
       </c>
       <c r="G137" t="s">
-        <v>141</v>
+        <v>438</v>
       </c>
       <c r="H137">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="I137" t="s">
-        <v>85</v>
-      </c>
-      <c r="J137" t="s">
-        <v>168</v>
-      </c>
-      <c r="K137" t="s">
-        <v>482</v>
-      </c>
-      <c r="L137" t="s">
-        <v>366</v>
-      </c>
-      <c r="M137" s="1">
-        <v>46304</v>
-      </c>
-      <c r="N137" t="s">
-        <v>529</v>
-      </c>
-      <c r="O137" t="s">
-        <v>478</v>
-      </c>
-      <c r="P137" t="s">
-        <v>567</v>
-      </c>
-      <c r="Q137" t="s">
-        <v>572</v>
+        <v>473</v>
       </c>
     </row>
     <row r="138" spans="1:17">
@@ -9931,7 +9848,7 @@
         <v>13</v>
       </c>
       <c r="B138" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C138" t="s">
         <v>25</v>
@@ -9940,19 +9857,43 @@
         <v>85</v>
       </c>
       <c r="E138" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F138" s="1">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="G138" t="s">
-        <v>443</v>
+        <v>140</v>
       </c>
       <c r="H138">
-        <v>23</v>
+        <v>144.5</v>
       </c>
       <c r="I138" t="s">
-        <v>478</v>
+        <v>85</v>
+      </c>
+      <c r="J138" t="s">
+        <v>166</v>
+      </c>
+      <c r="K138" t="s">
+        <v>477</v>
+      </c>
+      <c r="L138" t="s">
+        <v>361</v>
+      </c>
+      <c r="M138" s="1">
+        <v>46306</v>
+      </c>
+      <c r="N138" t="s">
+        <v>524</v>
+      </c>
+      <c r="O138" t="s">
+        <v>474</v>
+      </c>
+      <c r="P138" t="s">
+        <v>561</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="139" spans="1:17">
@@ -9960,7 +9901,7 @@
         <v>13</v>
       </c>
       <c r="B139" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C139" t="s">
         <v>25</v>
@@ -9969,19 +9910,19 @@
         <v>85</v>
       </c>
       <c r="E139" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="F139" s="1">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="G139" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="H139">
-        <v>23</v>
+        <v>56.1</v>
       </c>
       <c r="I139" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="140" spans="1:17">
@@ -9989,192 +9930,110 @@
         <v>13</v>
       </c>
       <c r="B140" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C140" t="s">
         <v>25</v>
       </c>
       <c r="D140" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E140" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F140" s="1">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="G140" t="s">
-        <v>142</v>
+        <v>440</v>
       </c>
       <c r="H140">
-        <v>144.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I140" t="s">
-        <v>86</v>
-      </c>
-      <c r="J140" t="s">
-        <v>168</v>
-      </c>
-      <c r="K140" t="s">
-        <v>483</v>
-      </c>
-      <c r="L140" t="s">
-        <v>366</v>
-      </c>
-      <c r="M140" s="1">
-        <v>46306</v>
-      </c>
-      <c r="N140" t="s">
-        <v>530</v>
-      </c>
-      <c r="O140" t="s">
-        <v>480</v>
-      </c>
-      <c r="P140" t="s">
-        <v>568</v>
-      </c>
-      <c r="Q140" t="s">
-        <v>571</v>
+        <v>475</v>
       </c>
     </row>
     <row r="141" spans="1:17">
       <c r="A141" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B141" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C141" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D141" t="s">
         <v>86</v>
       </c>
       <c r="E141" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F141" s="1">
-        <v>46306</v>
+        <v>46301</v>
       </c>
       <c r="G141" t="s">
-        <v>445</v>
+        <v>141</v>
       </c>
       <c r="H141">
-        <v>56.1</v>
+        <v>53.9</v>
       </c>
       <c r="I141" t="s">
-        <v>480</v>
+        <v>86</v>
+      </c>
+      <c r="J141" t="s">
+        <v>167</v>
+      </c>
+      <c r="K141" t="s">
+        <v>477</v>
+      </c>
+      <c r="L141" t="s">
+        <v>363</v>
+      </c>
+      <c r="M141" s="1">
+        <v>46301</v>
+      </c>
+      <c r="N141" t="s">
+        <v>141</v>
+      </c>
+      <c r="O141" t="s">
+        <v>347</v>
+      </c>
+      <c r="P141" t="s">
+        <v>562</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="142" spans="1:17">
       <c r="A142" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C142" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D142" t="s">
         <v>86</v>
       </c>
       <c r="E142" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="F142" s="1">
-        <v>46306</v>
+        <v>46301</v>
       </c>
       <c r="G142" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="H142">
-        <v>88.40000000000001</v>
+        <v>53.9</v>
       </c>
       <c r="I142" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="143" spans="1:17">
-      <c r="A143" t="s">
-        <v>12</v>
-      </c>
-      <c r="B143" t="s">
-        <v>364</v>
-      </c>
-      <c r="C143" t="s">
-        <v>26</v>
-      </c>
-      <c r="D143" t="s">
-        <v>87</v>
-      </c>
-      <c r="E143" t="s">
-        <v>367</v>
-      </c>
-      <c r="F143" s="1">
-        <v>46301</v>
-      </c>
-      <c r="G143" t="s">
-        <v>143</v>
-      </c>
-      <c r="H143">
-        <v>53.9</v>
-      </c>
-      <c r="I143" t="s">
-        <v>87</v>
-      </c>
-      <c r="J143" t="s">
-        <v>169</v>
-      </c>
-      <c r="K143" t="s">
-        <v>483</v>
-      </c>
-      <c r="L143" t="s">
-        <v>368</v>
-      </c>
-      <c r="M143" s="1">
-        <v>46301</v>
-      </c>
-      <c r="N143" t="s">
-        <v>143</v>
-      </c>
-      <c r="O143" t="s">
-        <v>352</v>
-      </c>
-      <c r="P143" t="s">
-        <v>569</v>
-      </c>
-      <c r="Q143" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="144" spans="1:17">
-      <c r="A144" t="s">
-        <v>12</v>
-      </c>
-      <c r="B144" t="s">
-        <v>365</v>
-      </c>
-      <c r="C144" t="s">
-        <v>26</v>
-      </c>
-      <c r="D144" t="s">
-        <v>87</v>
-      </c>
-      <c r="E144" t="s">
-        <v>368</v>
-      </c>
-      <c r="F144" s="1">
-        <v>46301</v>
-      </c>
-      <c r="G144" t="s">
-        <v>447</v>
-      </c>
-      <c r="H144">
-        <v>53.9</v>
-      </c>
-      <c r="I144" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
